--- a/gelato_flavors.xlsx
+++ b/gelato_flavors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC063E7A-B633-4349-A004-7438E8C824A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0817384A-A8AA-405D-9297-88747BB83D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="128">
   <si>
     <t>ALBICOCCA</t>
   </si>
@@ -121,9 +121,6 @@
     <t>NOCCIOLA</t>
   </si>
   <si>
-    <t>NOCI PECAN</t>
-  </si>
-  <si>
     <t>POLLICINA</t>
   </si>
   <si>
@@ -395,6 +392,18 @@
   </si>
   <si>
     <t>TOTAL:</t>
+  </si>
+  <si>
+    <t>P.LARNAKA</t>
+  </si>
+  <si>
+    <t>FAVE PECORINO</t>
+  </si>
+  <si>
+    <t>NOCI UVETTA</t>
+  </si>
+  <si>
+    <t>STRAWBERRY FILEDS</t>
   </si>
 </sst>
 </file>
@@ -483,11 +492,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -796,7 +805,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -812,593 +821,593 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="H1" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="B2" s="5"/>
       <c r="C2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="6"/>
+      <c r="D2" s="5"/>
       <c r="E2" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" s="6"/>
+        <v>75</v>
+      </c>
+      <c r="F2" s="5"/>
       <c r="G2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="6"/>
+      <c r="H2" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="B3" s="5"/>
       <c r="C3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="5"/>
       <c r="E3" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="F3" s="5"/>
       <c r="G3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="6"/>
+      <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="B4" s="5"/>
       <c r="C4" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="D4" s="5"/>
       <c r="E4" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F4" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="F4" s="5"/>
       <c r="G4" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="H4" s="6"/>
+        <v>117</v>
+      </c>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="5"/>
       <c r="C5" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="D5" s="5"/>
       <c r="E5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="6"/>
+        <v>78</v>
+      </c>
+      <c r="F5" s="5"/>
       <c r="G5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="6"/>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="6"/>
+        <v>44</v>
+      </c>
+      <c r="B6" s="5"/>
       <c r="C6" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="D6" s="5"/>
       <c r="E6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="F6" s="5"/>
       <c r="G6" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="H6" s="6"/>
+        <v>109</v>
+      </c>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="5"/>
       <c r="C7" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" s="6"/>
+        <v>95</v>
+      </c>
+      <c r="D7" s="5"/>
       <c r="E7" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F7" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="F7" s="5"/>
       <c r="G7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="6"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B8" s="6"/>
+        <v>94</v>
+      </c>
+      <c r="B8" s="5"/>
       <c r="C8" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" s="6"/>
+        <v>96</v>
+      </c>
+      <c r="D8" s="5"/>
       <c r="E8" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="6"/>
+        <v>81</v>
+      </c>
+      <c r="F8" s="5"/>
       <c r="G8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="6"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="B9" s="5"/>
       <c r="C9" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="6"/>
+        <v>108</v>
+      </c>
+      <c r="D9" s="5"/>
       <c r="E9" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="6"/>
+        <v>82</v>
+      </c>
+      <c r="F9" s="5"/>
       <c r="G9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="6"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="6"/>
+        <v>125</v>
+      </c>
+      <c r="B10" s="5"/>
       <c r="C10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F10" s="6"/>
+        <v>83</v>
+      </c>
+      <c r="F10" s="5"/>
       <c r="G10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H10" s="6"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B11" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="B11" s="5"/>
       <c r="C11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="6"/>
+        <v>43</v>
+      </c>
+      <c r="D11" s="5"/>
       <c r="E11" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F11" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="F11" s="5"/>
       <c r="G11" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H11" s="6"/>
+        <v>110</v>
+      </c>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B12" s="6"/>
+        <v>107</v>
+      </c>
+      <c r="B12" s="5"/>
       <c r="C12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="6"/>
+        <v>39</v>
+      </c>
+      <c r="D12" s="5"/>
       <c r="E12" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="6"/>
+        <v>85</v>
+      </c>
+      <c r="F12" s="5"/>
       <c r="G12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="6"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="6"/>
+      <c r="B13" s="5"/>
       <c r="C13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="D13" s="5"/>
       <c r="E13" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="6"/>
+        <v>86</v>
+      </c>
+      <c r="F13" s="5"/>
       <c r="G13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H13" s="6"/>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="B14" s="5"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="6"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F14" s="6"/>
+        <v>87</v>
+      </c>
+      <c r="F14" s="5"/>
       <c r="G14" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H14" s="6"/>
+        <v>114</v>
+      </c>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="6"/>
+        <v>27</v>
+      </c>
+      <c r="B15" s="5"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="6"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F15" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="F15" s="5"/>
       <c r="G15" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="H15" s="6"/>
+        <v>111</v>
+      </c>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="6"/>
+        <v>28</v>
+      </c>
+      <c r="B16" s="5"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="6"/>
+      <c r="D16" s="5"/>
       <c r="E16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="6"/>
+      <c r="F16" s="5"/>
       <c r="G16" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="H16" s="6"/>
+        <v>112</v>
+      </c>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="6"/>
+        <v>29</v>
+      </c>
+      <c r="B17" s="5"/>
       <c r="C17" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="6"/>
+        <v>53</v>
+      </c>
+      <c r="D17" s="5"/>
       <c r="E17" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F17" s="6"/>
+        <v>122</v>
+      </c>
+      <c r="F17" s="5"/>
       <c r="G17" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="6"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="B18" s="5"/>
       <c r="C18" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="6"/>
+        <v>65</v>
+      </c>
+      <c r="D18" s="5"/>
       <c r="E18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="6"/>
+      <c r="F18" s="5"/>
       <c r="G18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H18" s="6"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="6"/>
+        <v>31</v>
+      </c>
+      <c r="B19" s="5"/>
       <c r="C19" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="6"/>
+        <v>66</v>
+      </c>
+      <c r="D19" s="5"/>
       <c r="E19" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F19" s="6"/>
+        <v>121</v>
+      </c>
+      <c r="F19" s="5"/>
       <c r="G19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H19" s="6"/>
+      <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="6"/>
+        <v>52</v>
+      </c>
+      <c r="B20" s="5"/>
       <c r="C20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="6"/>
+        <v>67</v>
+      </c>
+      <c r="D20" s="5"/>
       <c r="E20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="6"/>
+      <c r="F20" s="5"/>
       <c r="G20" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H20" s="6"/>
+        <v>113</v>
+      </c>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21" s="6"/>
+        <v>32</v>
+      </c>
+      <c r="B21" s="5"/>
       <c r="C21" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="6"/>
+        <v>64</v>
+      </c>
+      <c r="D21" s="5"/>
       <c r="E21" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="6"/>
+      <c r="F21" s="5"/>
       <c r="G21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="6"/>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="6"/>
+        <v>97</v>
+      </c>
+      <c r="B22" s="5"/>
       <c r="C22" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="6"/>
+        <v>63</v>
+      </c>
+      <c r="D22" s="5"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="6"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B23" s="6"/>
+        <v>126</v>
+      </c>
+      <c r="B23" s="5"/>
       <c r="C23" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="6"/>
+        <v>62</v>
+      </c>
+      <c r="D23" s="5"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H23" s="6"/>
+        <v>42</v>
+      </c>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B24" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="B24" s="5"/>
       <c r="C24" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="6"/>
+        <v>46</v>
+      </c>
+      <c r="D24" s="5"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="6"/>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="B25" s="5"/>
       <c r="C25" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="6"/>
+        <v>56</v>
+      </c>
+      <c r="D25" s="5"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H25" s="6"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="6"/>
+        <v>124</v>
+      </c>
+      <c r="B26" s="5"/>
       <c r="C26" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="D26" s="5"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H26" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="6"/>
+        <v>100</v>
+      </c>
+      <c r="B27" s="5"/>
       <c r="C27" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="D27" s="5"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="H27" s="6"/>
+        <v>115</v>
+      </c>
+      <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B28" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="B28" s="5"/>
       <c r="C28" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" s="6"/>
+        <v>59</v>
+      </c>
+      <c r="D28" s="5"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H28" s="6"/>
+      <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="B29" s="5"/>
       <c r="C29" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="D29" s="5"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H29" s="6"/>
+        <v>116</v>
+      </c>
+      <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B30" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="B30" s="5"/>
       <c r="C30" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="D30" s="5"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="H30" s="6"/>
+        <v>118</v>
+      </c>
+      <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B31" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="B31" s="5"/>
       <c r="C31" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="6"/>
+        <v>60</v>
+      </c>
+      <c r="D31" s="5"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H31" s="6"/>
+        <v>69</v>
+      </c>
+      <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="6"/>
+        <v>103</v>
+      </c>
+      <c r="B32" s="5"/>
       <c r="C32" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="6"/>
+        <v>61</v>
+      </c>
+      <c r="D32" s="5"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H32" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="6"/>
+        <v>104</v>
+      </c>
+      <c r="B33" s="5"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="H33" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="H33" s="5"/>
     </row>
     <row r="34" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B34" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="B34" s="5"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="H34" s="6"/>
+        <v>120</v>
+      </c>
+      <c r="H34" s="5"/>
     </row>
     <row r="35" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B35" s="6"/>
+        <v>37</v>
+      </c>
+      <c r="B35" s="5"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -1408,13 +1417,13 @@
     </row>
     <row r="36" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D36" s="5"/>
+        <v>105</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" s="6"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
@@ -1422,11 +1431,11 @@
     </row>
     <row r="37" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
+        <v>106</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
@@ -1434,11 +1443,11 @@
     </row>
     <row r="38" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
+        <v>127</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
@@ -1446,15 +1455,30 @@
     </row>
     <row r="39" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
+        <v>38</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C18:C32">

--- a/gelato_flavors.xlsx
+++ b/gelato_flavors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -837,6 +837,9 @@
       <c r="A35" t="str">
         <v>SEADAS</v>
       </c>
+      <c r="G35" t="str">
+        <v>FRAGOLE CHAMP</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -845,6 +848,9 @@
       <c r="C36" t="str">
         <v>TOTAL:</v>
       </c>
+      <c r="G36" t="str">
+        <v>LIMONE &amp; BASILICO</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -879,6 +885,16 @@
     <row r="46">
       <c r="A46" t="str">
         <v>NOCI PECAN</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>BAKLAVA</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>PERA GORGONZOLA</v>
       </c>
     </row>
   </sheetData>
@@ -887,7 +903,7 @@
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H48"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/gelato_flavors.xlsx
+++ b/gelato_flavors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -525,7 +525,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>C.BANANA</v>
+        <v>C. BANANA</v>
       </c>
       <c r="C9" t="str">
         <v>C. ZENZERO</v>
@@ -895,6 +895,16 @@
     <row r="48">
       <c r="A48" t="str">
         <v>PERA GORGONZOLA</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>COCCO AL RUM</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>DRACARYS</v>
       </c>
     </row>
   </sheetData>
@@ -903,7 +913,7 @@
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/gelato_flavors.xlsx
+++ b/gelato_flavors.xlsx
@@ -1,52 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Flavors" sheetId="1" r:id="rId1"/>
+    <sheet name="Flavors" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,13 +42,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -396,515 +440,810 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H50"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Gelato</v>
-      </c>
-      <c r="B1" t="str">
-        <v>ORDINE</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Creme</v>
-      </c>
-      <c r="D1" t="str">
-        <v>ORDINE</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Cioccolati</v>
-      </c>
-      <c r="F1" t="str">
-        <v>ORDINE</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Sorbetti</v>
-      </c>
-      <c r="H1" t="str">
-        <v>ORDINE</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Gelato</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ORDINE</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ORDINE</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Cioccolati</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ORDINE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Sorbetti</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ORDINE</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>ARACHIDI</v>
-      </c>
-      <c r="C2" t="str">
-        <v>CARROT CAKE</v>
-      </c>
-      <c r="E2" t="str">
-        <v>C. AL LATTE GELATO</v>
-      </c>
-      <c r="G2" t="str">
-        <v>ALBICOCCA</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ARACHIDI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CARROT CAKE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>C. AL LATTE GELATO</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ALBICOCCA</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>BACIO</v>
-      </c>
-      <c r="C3" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
-      </c>
-      <c r="E3" t="str">
-        <v>C. AL PIMENTO</v>
-      </c>
-      <c r="G3" t="str">
-        <v>AMARENA</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BACIO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CHEESECAKE MIRTILLI</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>C. AL PIMENTO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>AMARENA</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>BASILICO</v>
-      </c>
-      <c r="C4" t="str">
-        <v>C. AGNESE</v>
-      </c>
-      <c r="E4" t="str">
-        <v>C. AL WHISKY</v>
-      </c>
-      <c r="G4" t="str">
-        <v>ANANAS</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BASILICO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C. AGNESE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C. AL WHISKY</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ANANAS</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>BIANCANEVE</v>
-      </c>
-      <c r="C5" t="str">
-        <v>C. CANNELLA</v>
-      </c>
-      <c r="E5" t="str">
-        <v>C. BIANCO</v>
-      </c>
-      <c r="G5" t="str">
-        <v>ANGURIA</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BIANCANEVE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C. CANNELLA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>C. BIANCO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ANGURIA</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>BUONGIORNO AMORE</v>
-      </c>
-      <c r="C6" t="str">
-        <v>C. FRAGOLE E MANDORLE</v>
-      </c>
-      <c r="E6" t="str">
-        <v>C. CRUDO DEL PERU'</v>
-      </c>
-      <c r="G6" t="str">
-        <v>AVOCADO</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BUONGIORNO AMORE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C. FRAGOLE E MANDORLE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C. CRUDO DEL PERU'</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AVOCADO</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>CAFFE'</v>
-      </c>
-      <c r="C7" t="str">
-        <v>C. PASTICCIERA PARISI</v>
-      </c>
-      <c r="E7" t="str">
-        <v>C. E ARANCIA</v>
-      </c>
-      <c r="G7" t="str">
-        <v>BANANA E LIME</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAFFE'</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C. PASTICCIERA PARISI</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C. E ARANCIA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>BANANA E LIME</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>COCCO C.</v>
-      </c>
-      <c r="C8" t="str">
-        <v>C. VANIGLIA</v>
-      </c>
-      <c r="E8" t="str">
-        <v>C. EQUADOR</v>
-      </c>
-      <c r="G8" t="str">
-        <v>CACHI</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>COCCO C.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C. VANIGLIA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>C. EQUADOR</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CACHI</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>C. BANANA</v>
-      </c>
-      <c r="C9" t="str">
-        <v>C. ZENZERO</v>
-      </c>
-      <c r="E9" t="str">
-        <v>C. KENTUCKY</v>
-      </c>
-      <c r="G9" t="str">
-        <v>COCONUT RICE CAKE</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C. BANANA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C. ZENZERO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>C. KENTUCKY</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>COCONUT RICE CAKE</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>FAVE FRESCHE &amp; PECORINO</v>
-      </c>
-      <c r="C10" t="str">
-        <v>LEMON CURD</v>
-      </c>
-      <c r="E10" t="str">
-        <v>C. LAPSANG SOUCHOUNG</v>
-      </c>
-      <c r="G10" t="str">
-        <v>FRAGOLA</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FAVE FRESCHE &amp; PECORINO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LEMON CURD</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>C. LAPSANG SOUCHOUNG</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>FRAGOLA</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>FIORDILATTE</v>
-      </c>
-      <c r="C11" t="str">
-        <v>SACRIPANTE</v>
-      </c>
-      <c r="E11" t="str">
-        <v>C. MADAGASCAR</v>
-      </c>
-      <c r="G11" t="str">
-        <v>FRUTTI DI BOSCO</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FIORDILATTE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SACRIPANTE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>C. MADAGASCAR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FRUTTI DI BOSCO</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>LAVANDA</v>
-      </c>
-      <c r="C12" t="str">
-        <v>TIRAMISU'</v>
-      </c>
-      <c r="E12" t="str">
-        <v>C. ROSEMARY</v>
-      </c>
-      <c r="G12" t="str">
-        <v>LAMPONI SORBETTO</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LAVANDA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TIRAMISU'</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>C. ROSEMARY</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LAMPONI SORBETTO</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>LATTE DI FICO</v>
-      </c>
-      <c r="C13" t="str">
-        <v>ZABAIONE GELATO</v>
-      </c>
-      <c r="E13" t="str">
-        <v>C. UGANDA</v>
-      </c>
-      <c r="G13" t="str">
-        <v>LIMONE</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LATTE DI FICO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ZABAIONE GELATO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>C. UGANDA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LIMONE</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>MENTA E C.</v>
-      </c>
-      <c r="E14" t="str">
-        <v>C. VENEZUELA</v>
-      </c>
-      <c r="G14" t="str">
-        <v>MANGO</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MENTA E C.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>C. VENEZUELA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MANGO</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>LIQUIRIZIA</v>
-      </c>
-      <c r="E15" t="str">
-        <v>C. WASABI</v>
-      </c>
-      <c r="G15" t="str">
-        <v>MELA M.C.</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LIQUIRIZIA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>C. WASABI</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MELA M.C.</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
-      </c>
-      <c r="E16" t="str">
-        <v>ESTASI</v>
-      </c>
-      <c r="G16" t="str">
-        <v>MELOGRANO</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MANDORLA AL CARDAMOMO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ESTASI</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MELOGRANO</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>MANDORLA BIANCA</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Varie</v>
-      </c>
-      <c r="E17" t="str">
-        <v>V. FIOR DI CIOCCOLATO</v>
-      </c>
-      <c r="G17" t="str">
-        <v>MELONE</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MANDORLA BIANCA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Varie</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>V. FIOR DI CIOCCOLATO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MELONE</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>MANDORLA E ARANCIA</v>
-      </c>
-      <c r="C18" t="str">
-        <v>CAPRESE</v>
-      </c>
-      <c r="E18" t="str">
-        <v>GIANDUIA</v>
-      </c>
-      <c r="G18" t="str">
-        <v>MIRTILLO</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MANDORLA E ARANCIA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CAPRESE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>GIANDUIA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MIRTILLO</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>MANDORLA TOSTATA</v>
-      </c>
-      <c r="C19" t="str">
-        <v>CHICCHIAINI</v>
-      </c>
-      <c r="E19" t="str">
-        <v>V. GIANDUIA VARIEGATA</v>
-      </c>
-      <c r="G19" t="str">
-        <v>MORA</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MANDORLA TOSTATA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CHICCHIAINI</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>V. GIANDUIA VARIEGATA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>MONTBLANC</v>
-      </c>
-      <c r="C20" t="str">
-        <v>CIOCCOLATA CALDA</v>
-      </c>
-      <c r="E20" t="str">
-        <v>MOU LATTE SALATO</v>
-      </c>
-      <c r="G20" t="str">
-        <v>PANACEA</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MONTBLANC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CIOCCOLATA CALDA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MOU LATTE SALATO</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>PANACEA</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>NOCCIOLA</v>
-      </c>
-      <c r="C21" t="str">
-        <v>COPPETTA GRANDE</v>
-      </c>
-      <c r="E21" t="str">
-        <v>SACHER TORTE</v>
-      </c>
-      <c r="G21" t="str">
-        <v>PAPAYA</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NOCCIOLA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>COPPETTA GRANDE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SACHER TORTE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>PAPAYA</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>NOCCIOLA BURRO</v>
-      </c>
-      <c r="C22" t="str">
-        <v>COPPETTA PICCOLA</v>
-      </c>
-      <c r="G22" t="str">
-        <v>PASSION FRUIT</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NOCCIOLA BURRO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>COPPETTA PICCOLA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>PASSION FRUIT</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>NOCI UVETTA</v>
-      </c>
-      <c r="C23" t="str">
-        <v>MOUSSE</v>
-      </c>
-      <c r="G23" t="str">
-        <v>PENSIERO</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NOCI UVETTA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MOUSSE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>PENSIERO</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>PEREBH</v>
-      </c>
-      <c r="C24" t="str">
-        <v>SUSHI GELATO</v>
-      </c>
-      <c r="G24" t="str">
-        <v>PERA</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PEREBH</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SUSHI GELATO</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>PERA</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>P.BRONTE</v>
-      </c>
-      <c r="C25" t="str">
-        <v>TORTA AGNESE 6P</v>
-      </c>
-      <c r="G25" t="str">
-        <v>PESCHE AL VINO</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P.BRONTE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TORTA AGNESE 6P</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>PESCHE AL VINO</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>PISTACCHIO LARNAKA</v>
-      </c>
-      <c r="C26" t="str">
-        <v>TORTA AGNESE 8P</v>
-      </c>
-      <c r="G26" t="str">
-        <v>PUNCH PARADISE</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PISTACCHIO LARNAKA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TORTA AGNESE 8P</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>PUNCH PARADISE</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>P. SIRIANO</v>
-      </c>
-      <c r="C27" t="str">
-        <v>TORTA CHEESCAKE 6P</v>
-      </c>
-      <c r="G27" t="str">
-        <v>ROSA E ARANCIA</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P. SIRIANO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TORTA CHEESCAKE 6P</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ROSA E ARANCIA</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>POLLICINA</v>
-      </c>
-      <c r="C28" t="str">
-        <v>TORTA CHEESCAKE 8P</v>
-      </c>
-      <c r="G28" t="str">
-        <v>UVA E NOCI</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>POLLICINA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TORTA CHEESCAKE 8P</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>UVA E NOCI</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>RICOTTA E AGRUMI</v>
-      </c>
-      <c r="C29" t="str">
-        <v>TORTA LAURA 6P</v>
-      </c>
-      <c r="G29" t="str">
-        <v>UVA FRAGOLA</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RICOTTA E AGRUMI</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TORTA LAURA 6P</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>UVA FRAGOLA</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>RICOTTA E FICHI</v>
-      </c>
-      <c r="C30" t="str">
-        <v>TORTA LAURA 8P</v>
-      </c>
-      <c r="G30" t="str">
-        <v>V. BANACHI</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RICOTTA E FICHI</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TORTA LAURA 8P</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>V. BANACHI</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>RICOTTA E PERA</v>
-      </c>
-      <c r="C31" t="str">
-        <v>TORTA TIRAMISU 6P</v>
-      </c>
-      <c r="G31" t="str">
-        <v>V. CASTAGNA AL WHISKY</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RICOTTA E PERA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TORTA TIRAMISU 6P</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>V. CASTAGNA AL WHISKY</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>RICOTTA E AMARENE</v>
-      </c>
-      <c r="C32" t="str">
-        <v>TORTA TIRAMISU 8P</v>
-      </c>
-      <c r="G32" t="str">
-        <v>V. CASTAGNA E MIRTO</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RICOTTA E AMARENE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TORTA TIRAMISU 8P</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>V. CASTAGNA E MIRTO</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>RICOTTA E COCCO</v>
-      </c>
-      <c r="G33" t="str">
-        <v>V.BRONTE GREEN</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RICOTTA E COCCO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>V.BRONTE GREEN</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>RISO E VANIGLIA</v>
-      </c>
-      <c r="G34" t="str">
-        <v>V. NOCCIOLA F.</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>RISO E VANIGLIA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>V. NOCCIOLA F.</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>SEADAS</v>
-      </c>
-      <c r="G35" t="str">
-        <v>FRAGOLE CHAMP</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SEADAS</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>FRAGOLE CHAMP</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>STRACCHINO PERA</v>
-      </c>
-      <c r="C36" t="str">
-        <v>TOTAL:</v>
-      </c>
-      <c r="G36" t="str">
-        <v>LIMONE &amp; BASILICO</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STRACCHINO PERA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TOTAL:</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>LIMONE &amp; BASILICO</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>STRACCHINO ALBICOCCHA</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STRACCHINO ALBICOCCHA</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>STRAWBERRY FIELD FOREVER</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STRAWBERRY FIELD FOREVER</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>STRACCIATELLA</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STRACCIATELLA</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>TE VERDE MATCHA</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TE VERDE MATCHA</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>VENERE ROSA</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>VENERE ROSA</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
-        <v>YOGURT</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>YOGURT</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
-        <v>NOCI PECAN</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NOCI PECAN</t>
+        </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
-        <v>BAKLAVA</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BAKLAVA</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="str">
-        <v>PERA GORGONZOLA</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PERA GORGONZOLA</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str">
-        <v>COCCO AL RUM</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>COCCO AL RUM</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="str">
-        <v>DRACARYS</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DRACARYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>FICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PAMPANELLA</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -912,8 +1251,5 @@
     <mergeCell ref="C36:D39"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
-  </ignoredErrors>
 </worksheet>
 </file>